--- a/hourly datasets/cap_gen_year10final.xlsx
+++ b/hourly datasets/cap_gen_year10final.xlsx
@@ -485,7 +485,7 @@
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="n">
-        <v>0.1025354202104953</v>
+        <v>0.09890440508437527</v>
       </c>
     </row>
     <row r="3">
@@ -495,7 +495,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.09438849744921556</v>
+        <v>0.09328693936976643</v>
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr"/>
@@ -503,7 +503,7 @@
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="n">
-        <v>0.1969239176597109</v>
+        <v>0.1921913444541417</v>
       </c>
     </row>
     <row r="4">
@@ -513,7 +513,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.07262270252128764</v>
+        <v>0.07139981715800713</v>
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr"/>
@@ -521,7 +521,7 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
-        <v>0.1751581227317829</v>
+        <v>0.1703042222423824</v>
       </c>
     </row>
     <row r="5">
@@ -531,7 +531,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.04880804554619359</v>
+        <v>0.04530251231263236</v>
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr"/>
@@ -539,7 +539,7 @@
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="n">
-        <v>0.1513434657566889</v>
+        <v>0.1442069173970076</v>
       </c>
     </row>
     <row r="6">
@@ -549,7 +549,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.03060681022136408</v>
+        <v>0.02597737618370236</v>
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr"/>
@@ -557,7 +557,7 @@
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="n">
-        <v>0.1331422304318594</v>
+        <v>0.1248817812680776</v>
       </c>
     </row>
     <row r="7">
@@ -567,25 +567,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.01967513280245653</v>
+        <v>0.01320687215838411</v>
       </c>
       <c r="C7" t="n">
-        <v>0.002401627296344176</v>
+        <v>0.001024285187167184</v>
       </c>
       <c r="D7" t="n">
-        <v>2.025554899249398</v>
+        <v>1.735778453472988</v>
       </c>
       <c r="E7" t="n">
-        <v>0.01094939379502432</v>
+        <v>0.005831628284193275</v>
       </c>
       <c r="F7" t="n">
-        <v>0.01495807827251136</v>
+        <v>0.0111981807296025</v>
       </c>
       <c r="G7" t="n">
-        <v>0.02439218733240197</v>
+        <v>0.01521556358716575</v>
       </c>
       <c r="H7" t="n">
-        <v>0.1222105530129518</v>
+        <v>0.1121112772427594</v>
       </c>
     </row>
     <row r="8">
@@ -595,25 +595,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.01880783187435991</v>
+        <v>0.0126111796282514</v>
       </c>
       <c r="C8" t="n">
-        <v>0.002530411786938378</v>
+        <v>0.001157254452995137</v>
       </c>
       <c r="D8" t="n">
-        <v>2.015292309059852</v>
+        <v>1.6970646996134</v>
       </c>
       <c r="E8" t="n">
-        <v>0.007783556192342187</v>
+        <v>0.005079915201244837</v>
       </c>
       <c r="F8" t="n">
-        <v>0.01382927390775375</v>
+        <v>0.01033495891780807</v>
       </c>
       <c r="G8" t="n">
-        <v>0.02378638984096626</v>
+        <v>0.01488740033869482</v>
       </c>
       <c r="H8" t="n">
-        <v>0.1213432520848552</v>
+        <v>0.1115155847126267</v>
       </c>
     </row>
     <row r="9">
@@ -623,25 +623,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.01782325126250029</v>
+        <v>0.01041681692697584</v>
       </c>
       <c r="C9" t="n">
-        <v>0.002140609952760626</v>
+        <v>0.0008396497052208686</v>
       </c>
       <c r="D9" t="n">
-        <v>1.774552441494788</v>
+        <v>1.453048241936528</v>
       </c>
       <c r="E9" t="n">
-        <v>0.004373944970796132</v>
+        <v>0.002300053201784215</v>
       </c>
       <c r="F9" t="n">
-        <v>0.01362314459485887</v>
+        <v>0.008769982587838447</v>
       </c>
       <c r="G9" t="n">
-        <v>0.02202335793014191</v>
+        <v>0.01206365126611382</v>
       </c>
       <c r="H9" t="n">
-        <v>0.1203586714729956</v>
+        <v>0.1093212220113511</v>
       </c>
     </row>
     <row r="10">
@@ -651,25 +651,25 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.01781243772760065</v>
+        <v>0.01044689079120411</v>
       </c>
       <c r="C10" t="n">
-        <v>0.001993052578255619</v>
+        <v>0.0008400894565043622</v>
       </c>
       <c r="D10" t="n">
-        <v>1.608405485260382</v>
+        <v>1.347974353969866</v>
       </c>
       <c r="E10" t="n">
-        <v>0.005759683438276856</v>
+        <v>0.003671726392333889</v>
       </c>
       <c r="F10" t="n">
-        <v>0.01389698689346763</v>
+        <v>0.008793994304394251</v>
       </c>
       <c r="G10" t="n">
-        <v>0.02172788856173453</v>
+        <v>0.01209978727801374</v>
       </c>
       <c r="H10" t="n">
-        <v>0.120347857938096</v>
+        <v>0.1093512958755794</v>
       </c>
     </row>
     <row r="11">
@@ -679,7 +679,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.03045470186181892</v>
+        <v>0.02895009198520828</v>
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr"/>
@@ -687,7 +687,7 @@
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="n">
-        <v>0.1329901220723142</v>
+        <v>0.1278544970695835</v>
       </c>
     </row>
     <row r="12">
@@ -697,7 +697,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.05251030857758803</v>
+        <v>0.04920256824361167</v>
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr"/>
@@ -705,7 +705,7 @@
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="n">
-        <v>0.1550457287880833</v>
+        <v>0.1481069733279869</v>
       </c>
     </row>
     <row r="13">
@@ -715,7 +715,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.06517608269330417</v>
+        <v>0.06174183833320879</v>
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr"/>
@@ -723,7 +723,7 @@
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="n">
-        <v>0.1677115029037995</v>
+        <v>0.1606462434175841</v>
       </c>
     </row>
     <row r="14">
@@ -733,7 +733,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.07306994158361906</v>
+        <v>0.07006579709827042</v>
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr"/>
@@ -741,7 +741,7 @@
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="n">
-        <v>0.1756053617941144</v>
+        <v>0.1689702021826457</v>
       </c>
     </row>
     <row r="15">
@@ -751,7 +751,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.08049854346949885</v>
+        <v>0.07692602749453045</v>
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr"/>
@@ -759,7 +759,7 @@
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="n">
-        <v>0.1830339636799942</v>
+        <v>0.1758304325789057</v>
       </c>
     </row>
     <row r="16">
@@ -769,7 +769,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.08373282897400397</v>
+        <v>0.08005604150727454</v>
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr"/>
@@ -777,7 +777,7 @@
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="n">
-        <v>0.1862682491844993</v>
+        <v>0.1789604465916498</v>
       </c>
     </row>
     <row r="17">
@@ -787,7 +787,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.08495449961570588</v>
+        <v>0.08138854805727225</v>
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr"/>
@@ -795,7 +795,7 @@
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="n">
-        <v>0.1874899198262012</v>
+        <v>0.1802929531416475</v>
       </c>
     </row>
     <row r="18">
@@ -805,22 +805,22 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-0.1025354202104953</v>
+        <v>-0.09890440508437527</v>
       </c>
       <c r="C18" t="n">
-        <v>0.008773877970870389</v>
+        <v>0.008201439859164297</v>
       </c>
       <c r="D18" t="n">
-        <v>-147864385954.2316</v>
+        <v>-144557375243.2826</v>
       </c>
       <c r="E18" t="n">
-        <v>0.03158185907953013</v>
+        <v>0.03172932583324374</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.1197770267284051</v>
+        <v>-0.115017372505689</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.08529381369258568</v>
+        <v>-0.08279143766306156</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
@@ -833,7 +833,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.08524194045651438</v>
+        <v>0.08217331480257573</v>
       </c>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr"/>
@@ -841,7 +841,7 @@
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="n">
-        <v>0.1877773606670097</v>
+        <v>0.181077719886951</v>
       </c>
     </row>
     <row r="20">
@@ -851,7 +851,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.09045507513899632</v>
+        <v>0.08656024408531059</v>
       </c>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr"/>
@@ -859,7 +859,7 @@
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="n">
-        <v>0.1929904953494916</v>
+        <v>0.1854646491696859</v>
       </c>
     </row>
     <row r="21">
@@ -869,7 +869,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.09267026568961423</v>
+        <v>0.08833127194220984</v>
       </c>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr"/>
@@ -877,7 +877,7 @@
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="n">
-        <v>0.1952056859001096</v>
+        <v>0.1872356770265851</v>
       </c>
     </row>
     <row r="22">
@@ -887,7 +887,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.09445513381055611</v>
+        <v>0.09212892322239817</v>
       </c>
       <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr"/>
@@ -895,7 +895,7 @@
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="n">
-        <v>0.1969905540210514</v>
+        <v>0.1910333283067734</v>
       </c>
     </row>
     <row r="23">
@@ -905,25 +905,15 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.1003439645995695</v>
-      </c>
-      <c r="C23" t="n">
-        <v>0.007970831847943354</v>
-      </c>
-      <c r="D23" t="n">
-        <v>1596169204495.518</v>
-      </c>
-      <c r="E23" t="n">
-        <v>0.04506884183514018</v>
-      </c>
-      <c r="F23" t="n">
-        <v>0.08466526849088823</v>
-      </c>
-      <c r="G23" t="n">
-        <v>0.116022660708251</v>
-      </c>
+        <v>0.09717804889418574</v>
+      </c>
+      <c r="C23" t="inlineStr"/>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr"/>
       <c r="H23" t="n">
-        <v>0.2028793848100648</v>
+        <v>0.196082453978561</v>
       </c>
     </row>
     <row r="24">
@@ -933,25 +923,25 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.1016688522498076</v>
+        <v>0.09921301293382936</v>
       </c>
       <c r="C24" t="n">
-        <v>0.00761966757086134</v>
+        <v>0.007360237638830239</v>
       </c>
       <c r="D24" t="n">
-        <v>970354239318.228</v>
+        <v>949116911907.7867</v>
       </c>
       <c r="E24" t="n">
-        <v>0.04728213471158763</v>
+        <v>0.04750342535379438</v>
       </c>
       <c r="F24" t="n">
-        <v>0.08669501588202619</v>
+        <v>0.08474684681050441</v>
       </c>
       <c r="G24" t="n">
-        <v>0.1166426886175892</v>
+        <v>0.1136791790571546</v>
       </c>
       <c r="H24" t="n">
-        <v>0.2042042724603029</v>
+        <v>0.1981174180182046</v>
       </c>
     </row>
     <row r="25">
@@ -961,25 +951,25 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.1030306421282219</v>
+        <v>0.1006499928344381</v>
       </c>
       <c r="C25" t="n">
-        <v>0.00810560903366833</v>
+        <v>0.007592852612510262</v>
       </c>
       <c r="D25" t="n">
-        <v>3111251340495.385</v>
+        <v>3045590823565.794</v>
       </c>
       <c r="E25" t="n">
-        <v>0.05795883556857434</v>
+        <v>0.05485799277833593</v>
       </c>
       <c r="F25" t="n">
-        <v>0.08708429616865478</v>
+        <v>0.0857188596596432</v>
       </c>
       <c r="G25" t="n">
-        <v>0.1189769880877886</v>
+        <v>0.1155811260092331</v>
       </c>
       <c r="H25" t="n">
-        <v>0.2055660623387172</v>
+        <v>0.1995543979188134</v>
       </c>
     </row>
     <row r="26">
@@ -989,7 +979,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.1052088270725087</v>
+        <v>0.102991104109221</v>
       </c>
       <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr"/>
@@ -997,7 +987,7 @@
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr"/>
       <c r="H26" t="n">
-        <v>0.207744247283004</v>
+        <v>0.2018955091935963</v>
       </c>
     </row>
     <row r="27">
@@ -1007,25 +997,25 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.1056437687550505</v>
+        <v>0.1040274310824261</v>
       </c>
       <c r="C27" t="n">
-        <v>0.00829279257810839</v>
+        <v>0.007760293315339699</v>
       </c>
       <c r="D27" t="n">
-        <v>1126179147947.119</v>
+        <v>1102159790778.847</v>
       </c>
       <c r="E27" t="n">
-        <v>0.07498685944630981</v>
+        <v>0.07009736870310823</v>
       </c>
       <c r="F27" t="n">
-        <v>0.08933459140845156</v>
+        <v>0.08876869266524105</v>
       </c>
       <c r="G27" t="n">
-        <v>0.1219529461016493</v>
+        <v>0.1192861694996116</v>
       </c>
       <c r="H27" t="n">
-        <v>0.2081791889655458</v>
+        <v>0.2029318361668013</v>
       </c>
     </row>
     <row r="28">
@@ -1035,25 +1025,25 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.102342716796393</v>
+        <v>0.1008686478980727</v>
       </c>
       <c r="C28" t="n">
-        <v>0.007681622173093967</v>
+        <v>0.007202779929977447</v>
       </c>
       <c r="D28" t="n">
-        <v>20.44270115233925</v>
+        <v>20.86220396419263</v>
       </c>
       <c r="E28" t="n">
-        <v>0.1177495005018594</v>
+        <v>0.1144655848073501</v>
       </c>
       <c r="F28" t="n">
-        <v>0.08725755755123202</v>
+        <v>0.08672317217002405</v>
       </c>
       <c r="G28" t="n">
-        <v>0.1174278760415537</v>
+        <v>0.1150141236261213</v>
       </c>
       <c r="H28" t="n">
-        <v>0.2048781370068883</v>
+        <v>0.199773052982448</v>
       </c>
     </row>
     <row r="29">
@@ -1063,25 +1053,25 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.01956145910228603</v>
+        <v>0.01144769404208244</v>
       </c>
       <c r="C29" t="n">
-        <v>0.002134752326741195</v>
+        <v>0.0009119904573380958</v>
       </c>
       <c r="D29" t="n">
-        <v>2.201256146179134</v>
+        <v>1.595907520450935</v>
       </c>
       <c r="E29" t="n">
-        <v>0.009606414221899074</v>
+        <v>0.008473662696813202</v>
       </c>
       <c r="F29" t="n">
-        <v>0.01535772402258803</v>
+        <v>0.009651906920272865</v>
       </c>
       <c r="G29" t="n">
-        <v>0.02376519418198398</v>
+        <v>0.0132434811638918</v>
       </c>
       <c r="H29" t="n">
-        <v>0.1220968793127813</v>
+        <v>0.1103520991264577</v>
       </c>
     </row>
   </sheetData>

--- a/hourly datasets/cap_gen_year10final.xlsx
+++ b/hourly datasets/cap_gen_year10final.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H29"/>
+  <dimension ref="A1:I29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,6 +466,11 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
+          <t>first_seen_iter</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
           <t>coef_pos</t>
         </is>
       </c>
@@ -477,7 +482,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>0.2321900331844568</v>
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr"/>
@@ -485,7 +490,10 @@
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="n">
-        <v>0.09890440508437527</v>
+        <v>4</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.09844929206413833</v>
       </c>
     </row>
     <row r="3">
@@ -495,7 +503,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.09328693936976643</v>
+        <v>0.3733313462120504</v>
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr"/>
@@ -503,7 +511,10 @@
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="n">
-        <v>0.1921913444541417</v>
+        <v>1</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.2395906050917319</v>
       </c>
     </row>
     <row r="4">
@@ -513,7 +524,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.07139981715800713</v>
+        <v>0.379402562639259</v>
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr"/>
@@ -521,7 +532,10 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
-        <v>0.1703042222423824</v>
+        <v>2</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.2456618215189405</v>
       </c>
     </row>
     <row r="5">
@@ -531,7 +545,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.04530251231263236</v>
+        <v>0.3887836838294945</v>
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr"/>
@@ -539,7 +553,10 @@
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="n">
-        <v>0.1442069173970076</v>
+        <v>7</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.255042942709176</v>
       </c>
     </row>
     <row r="6">
@@ -549,7 +566,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.02597737618370236</v>
+        <v>0.4066106206082252</v>
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr"/>
@@ -557,7 +574,10 @@
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="n">
-        <v>0.1248817812680776</v>
+        <v>7</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.2728698794879066</v>
       </c>
     </row>
     <row r="7">
@@ -567,25 +587,28 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.01320687215838411</v>
+        <v>0.3655711685137233</v>
       </c>
       <c r="C7" t="n">
-        <v>0.001024285187167184</v>
+        <v>0.009483703236250753</v>
       </c>
       <c r="D7" t="n">
-        <v>1.735778453472988</v>
+        <v>23.72449772852447</v>
       </c>
       <c r="E7" t="n">
-        <v>0.005831628284193275</v>
+        <v>0.006494031222657913</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0111981807296025</v>
+        <v>0.2041222133443643</v>
       </c>
       <c r="G7" t="n">
-        <v>0.01521556358716575</v>
+        <v>0.2413081978063322</v>
       </c>
       <c r="H7" t="n">
-        <v>0.1121112772427594</v>
+        <v>61</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.2318304273934048</v>
       </c>
     </row>
     <row r="8">
@@ -595,25 +618,28 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.0126111796282514</v>
+        <v>0.3626781510156257</v>
       </c>
       <c r="C8" t="n">
-        <v>0.001157254452995137</v>
+        <v>0.01022132969004657</v>
       </c>
       <c r="D8" t="n">
-        <v>1.6970646996134</v>
+        <v>23.03830168829519</v>
       </c>
       <c r="E8" t="n">
-        <v>0.005079915201244837</v>
+        <v>0.00566724937576183</v>
       </c>
       <c r="F8" t="n">
-        <v>0.01033495891780807</v>
+        <v>0.2042426462254789</v>
       </c>
       <c r="G8" t="n">
-        <v>0.01488740033869482</v>
+        <v>0.2443354509235914</v>
       </c>
       <c r="H8" t="n">
-        <v>0.1115155847126267</v>
+        <v>61</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.2289374098953072</v>
       </c>
     </row>
     <row r="9">
@@ -623,25 +649,28 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.01041681692697584</v>
+        <v>0.3664018741109902</v>
       </c>
       <c r="C9" t="n">
-        <v>0.0008396497052208686</v>
+        <v>0.009328392214838348</v>
       </c>
       <c r="D9" t="n">
-        <v>1.453048241936528</v>
+        <v>25.06299925412556</v>
       </c>
       <c r="E9" t="n">
-        <v>0.002300053201784215</v>
+        <v>0.002604070058553379</v>
       </c>
       <c r="F9" t="n">
-        <v>0.008769982587838447</v>
+        <v>0.2110600002474601</v>
       </c>
       <c r="G9" t="n">
-        <v>0.01206365126611382</v>
+        <v>0.2476376452901255</v>
       </c>
       <c r="H9" t="n">
-        <v>0.1093212220113511</v>
+        <v>61</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.2326611329906717</v>
       </c>
     </row>
     <row r="10">
@@ -651,25 +680,28 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.01044689079120411</v>
+        <v>0.3727717539287212</v>
       </c>
       <c r="C10" t="n">
-        <v>0.0008400894565043622</v>
+        <v>0.009619791553009429</v>
       </c>
       <c r="D10" t="n">
-        <v>1.347974353969866</v>
+        <v>25.30845133882353</v>
       </c>
       <c r="E10" t="n">
-        <v>0.003671726392333889</v>
+        <v>0.004076936090953681</v>
       </c>
       <c r="F10" t="n">
-        <v>0.008793994304394251</v>
+        <v>0.2199905265415897</v>
       </c>
       <c r="G10" t="n">
-        <v>0.01209978727801374</v>
+        <v>0.2577216350532876</v>
       </c>
       <c r="H10" t="n">
-        <v>0.1093512958755794</v>
+        <v>61</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.2390310128084027</v>
       </c>
     </row>
     <row r="11">
@@ -679,7 +711,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.02895009198520828</v>
+        <v>0.2699300949271028</v>
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr"/>
@@ -687,7 +719,10 @@
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="n">
-        <v>0.1278544970695835</v>
+        <v>1</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.1361893538067843</v>
       </c>
     </row>
     <row r="12">
@@ -697,7 +732,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.04920256824361167</v>
+        <v>0.2934648193945685</v>
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr"/>
@@ -705,7 +740,10 @@
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="n">
-        <v>0.1481069733279869</v>
+        <v>1</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.15972407827425</v>
       </c>
     </row>
     <row r="13">
@@ -715,7 +753,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.06174183833320879</v>
+        <v>0.3083793920003156</v>
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr"/>
@@ -723,7 +761,10 @@
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="n">
-        <v>0.1606462434175841</v>
+        <v>1</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.1746386508799971</v>
       </c>
     </row>
     <row r="14">
@@ -733,7 +774,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.07006579709827042</v>
+        <v>0.3185177361723515</v>
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr"/>
@@ -741,7 +782,10 @@
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="n">
-        <v>0.1689702021826457</v>
+        <v>1</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.184776995052033</v>
       </c>
     </row>
     <row r="15">
@@ -751,7 +795,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.07692602749453045</v>
+        <v>0.3258291361509715</v>
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr"/>
@@ -759,7 +803,10 @@
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="n">
-        <v>0.1758304325789057</v>
+        <v>1</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.192088395030653</v>
       </c>
     </row>
     <row r="16">
@@ -769,7 +816,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.08005604150727454</v>
+        <v>0.3303873205618342</v>
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr"/>
@@ -777,7 +824,10 @@
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="n">
-        <v>0.1789604465916498</v>
+        <v>1</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.1966465794415157</v>
       </c>
     </row>
     <row r="17">
@@ -787,7 +837,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.08138854805727225</v>
+        <v>0.3349882425424673</v>
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr"/>
@@ -795,7 +845,10 @@
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="n">
-        <v>0.1802929531416475</v>
+        <v>1</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.2012475014221488</v>
       </c>
     </row>
     <row r="18">
@@ -805,24 +858,27 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-0.09890440508437527</v>
+        <v>0.1337407411203185</v>
       </c>
       <c r="C18" t="n">
-        <v>0.008201439859164297</v>
+        <v>0.008453229745622046</v>
       </c>
       <c r="D18" t="n">
-        <v>-144557375243.2826</v>
+        <v>-145003444983.167</v>
       </c>
       <c r="E18" t="n">
-        <v>0.03172932583324374</v>
+        <v>0.03222925168746864</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.115017372505689</v>
+        <v>-0.1201269697115726</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.08279143766306156</v>
+        <v>-0.0869129870297411</v>
       </c>
       <c r="H18" t="n">
+        <v>5</v>
+      </c>
+      <c r="I18" t="n">
         <v>0</v>
       </c>
     </row>
@@ -833,7 +889,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.08217331480257573</v>
+        <v>0.3357376888598896</v>
       </c>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr"/>
@@ -841,7 +897,10 @@
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="n">
-        <v>0.181077719886951</v>
+        <v>1</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0.2019969477395711</v>
       </c>
     </row>
     <row r="20">
@@ -851,7 +910,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.08656024408531059</v>
+        <v>0.3394759491137586</v>
       </c>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr"/>
@@ -859,7 +918,10 @@
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="n">
-        <v>0.1854646491696859</v>
+        <v>1</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0.2057352079934401</v>
       </c>
     </row>
     <row r="21">
@@ -869,7 +931,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.08833127194220984</v>
+        <v>0.3418001963310667</v>
       </c>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr"/>
@@ -877,7 +939,10 @@
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="n">
-        <v>0.1872356770265851</v>
+        <v>1</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0.2080594552107482</v>
       </c>
     </row>
     <row r="22">
@@ -887,7 +952,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.09212892322239817</v>
+        <v>0.3477288279187588</v>
       </c>
       <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr"/>
@@ -895,7 +960,10 @@
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="n">
-        <v>0.1910333283067734</v>
+        <v>1</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0.2139880867984403</v>
       </c>
     </row>
     <row r="23">
@@ -905,7 +973,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.09717804889418574</v>
+        <v>0.3543826004283664</v>
       </c>
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr"/>
@@ -913,7 +981,10 @@
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="n">
-        <v>0.196082453978561</v>
+        <v>1</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.2206418593080479</v>
       </c>
     </row>
     <row r="24">
@@ -923,25 +994,28 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.09921301293382936</v>
+        <v>0.3607133185396891</v>
       </c>
       <c r="C24" t="n">
-        <v>0.007360237638830239</v>
+        <v>0.007346349965249768</v>
       </c>
       <c r="D24" t="n">
-        <v>949116911907.7867</v>
+        <v>949098123247.7306</v>
       </c>
       <c r="E24" t="n">
-        <v>0.04750342535379438</v>
+        <v>0.0474502030166368</v>
       </c>
       <c r="F24" t="n">
-        <v>0.08474684681050441</v>
+        <v>0.08462531083886539</v>
       </c>
       <c r="G24" t="n">
-        <v>0.1136791790571546</v>
+        <v>0.1135030600452222</v>
       </c>
       <c r="H24" t="n">
-        <v>0.1981174180182046</v>
+        <v>1</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.2269725774193706</v>
       </c>
     </row>
     <row r="25">
@@ -951,25 +1025,28 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.1006499928344381</v>
+        <v>0.3636353110201581</v>
       </c>
       <c r="C25" t="n">
-        <v>0.007592852612510262</v>
+        <v>0.007583322355193793</v>
       </c>
       <c r="D25" t="n">
-        <v>3045590823565.794</v>
+        <v>3045528234087.303</v>
       </c>
       <c r="E25" t="n">
-        <v>0.05485799277833593</v>
+        <v>0.05482098503152986</v>
       </c>
       <c r="F25" t="n">
-        <v>0.0857188596596432</v>
+        <v>0.08559467550810536</v>
       </c>
       <c r="G25" t="n">
-        <v>0.1155811260092331</v>
+        <v>0.1154194782462051</v>
       </c>
       <c r="H25" t="n">
-        <v>0.1995543979188134</v>
+        <v>1</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0.2298945698998396</v>
       </c>
     </row>
     <row r="26">
@@ -979,7 +1056,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.102991104109221</v>
+        <v>0.3690827937741919</v>
       </c>
       <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr"/>
@@ -987,7 +1064,10 @@
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr"/>
       <c r="H26" t="n">
-        <v>0.2018955091935963</v>
+        <v>1</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0.2353420526538734</v>
       </c>
     </row>
     <row r="27">
@@ -997,25 +1077,28 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.1040274310824261</v>
+        <v>0.3728823722201418</v>
       </c>
       <c r="C27" t="n">
-        <v>0.007760293315339699</v>
+        <v>0.007710312810241536</v>
       </c>
       <c r="D27" t="n">
-        <v>1102159790778.847</v>
+        <v>1102128340240.408</v>
       </c>
       <c r="E27" t="n">
-        <v>0.07009736870310823</v>
+        <v>0.0697031373442229</v>
       </c>
       <c r="F27" t="n">
-        <v>0.08876869266524105</v>
+        <v>0.08852762141047694</v>
       </c>
       <c r="G27" t="n">
-        <v>0.1192861694996116</v>
+        <v>0.1188487220494094</v>
       </c>
       <c r="H27" t="n">
-        <v>0.2029318361668013</v>
+        <v>1</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0.2391416310998233</v>
       </c>
     </row>
     <row r="28">
@@ -1025,25 +1108,28 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.1008686478980727</v>
+        <v>0.3746797350308845</v>
       </c>
       <c r="C28" t="n">
-        <v>0.007202779929977447</v>
+        <v>0.007099378034271893</v>
       </c>
       <c r="D28" t="n">
-        <v>20.86220396419263</v>
+        <v>20.79506148925729</v>
       </c>
       <c r="E28" t="n">
-        <v>0.1144655848073501</v>
+        <v>0.1098558940129009</v>
       </c>
       <c r="F28" t="n">
-        <v>0.08672317217002405</v>
+        <v>0.08647561564161396</v>
       </c>
       <c r="G28" t="n">
-        <v>0.1150141236261213</v>
+        <v>0.1143602817457388</v>
       </c>
       <c r="H28" t="n">
-        <v>0.199773052982448</v>
+        <v>1</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0.240938993910566</v>
       </c>
     </row>
     <row r="29">
@@ -1053,25 +1139,28 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.01144769404208244</v>
+        <v>0.368039217761586</v>
       </c>
       <c r="C29" t="n">
-        <v>0.0009119904573380958</v>
+        <v>0.009094489515321585</v>
       </c>
       <c r="D29" t="n">
-        <v>1.595907520450935</v>
+        <v>25.32193378829341</v>
       </c>
       <c r="E29" t="n">
-        <v>0.008473662696813202</v>
+        <v>0.01198873124225697</v>
       </c>
       <c r="F29" t="n">
-        <v>0.009651906920272865</v>
+        <v>0.2098039319579399</v>
       </c>
       <c r="G29" t="n">
-        <v>0.0132434811638918</v>
+        <v>0.2454795900880005</v>
       </c>
       <c r="H29" t="n">
-        <v>0.1103520991264577</v>
+        <v>61</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0.2342984766412675</v>
       </c>
     </row>
   </sheetData>
